--- a/Diarias/CustoPcabeça.xlsx
+++ b/Diarias/CustoPcabeça.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2902B4-EB36-43DA-9D47-7F78373EBDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F78AB0-02BD-4156-AB43-60375EB888B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5B15AADF-5E25-4D61-AF8C-F30613BBBE1E}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +62,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -107,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +121,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,10 +456,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FFC350-4118-4C33-8D35-869EA70857B4}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -541,7 +549,9 @@
       <c r="B3" s="4">
         <v>109.16935630099728</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4">
+        <v>97.918251852933665</v>
+      </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -559,6 +569,15 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" s="3"/>
     </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E13" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Diarias/CustoPcabeça.xlsx
+++ b/Diarias/CustoPcabeça.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F78AB0-02BD-4156-AB43-60375EB888B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E6226E-D14E-414B-856D-BD723031B925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5B15AADF-5E25-4D61-AF8C-F30613BBBE1E}"/>
   </bookViews>
@@ -552,7 +552,9 @@
       <c r="C3" s="4">
         <v>97.918251852933665</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4">
+        <v>129.25034567218427</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -577,6 +579,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Diarias/CustoPcabeça.xlsx
+++ b/Diarias/CustoPcabeça.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E6226E-D14E-414B-856D-BD723031B925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1649B0EB-41E2-4259-A98C-5F587BE9040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5B15AADF-5E25-4D61-AF8C-F30613BBBE1E}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +62,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -122,6 +128,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,7 +560,7 @@
         <v>97.918251852933665</v>
       </c>
       <c r="D3" s="4">
-        <v>129.25034567218427</v>
+        <v>133.66864852052305</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -571,6 +578,9 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" s="3"/>
     </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D8" s="6"/>
+    </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E11" s="5"/>
     </row>

--- a/Diarias/CustoPcabeça.xlsx
+++ b/Diarias/CustoPcabeça.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1649B0EB-41E2-4259-A98C-5F587BE9040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089361DF-4C93-46C4-B6EB-6CFCB3F2C3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5B15AADF-5E25-4D61-AF8C-F30613BBBE1E}"/>
   </bookViews>
@@ -467,7 +467,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -562,7 +562,9 @@
       <c r="D3" s="4">
         <v>133.66864852052305</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <v>126.04780949985326</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -577,9 +579,14 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" s="3"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D8" s="6"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E11" s="5"/>
